--- a/words/words.xlsx
+++ b/words/words.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\draem\Dropbox\100_Documents\320_【自己啓発】勉強\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://robocip20-my.sharepoint.com/personal/endo_tatsuya_robocip_or_jp/Documents/ドキュメント/_repos/other/words/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20904ACC-9A47-4E59-9D0C-A08BD8E602D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{20904ACC-9A47-4E59-9D0C-A08BD8E602D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD63D33C-37C8-47ED-B819-5646EB372992}"/>
   <bookViews>
-    <workbookView xWindow="-32385" yWindow="1230" windowWidth="32385" windowHeight="40695" xr2:uid="{5F4F135C-1501-4C2F-B795-058F7C491BB1}"/>
+    <workbookView xWindow="28815" yWindow="-6795" windowWidth="38385" windowHeight="42465" xr2:uid="{5F4F135C-1501-4C2F-B795-058F7C491BB1}"/>
   </bookViews>
   <sheets>
     <sheet name="用語集" sheetId="2" r:id="rId1"/>
@@ -18,17 +18,28 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">用語集!$A$1:$N$501</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3246" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3256" uniqueCount="373">
   <si>
     <t xml:space="preserve">No
 </t>
@@ -1454,34 +1465,6 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>ロングテール</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>https://ja.wikipedia.org/wiki/%E3%83%AD%E3%83%B3%E3%82%B0%E3%83%86%E3%83%BC%E3%83%AB#%E9%96%A2%E9%80%A3%E9%A0%85%E7%9B%AE</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>販売機会の少ない商品でもアイテム数を幅広く取り揃えること。
-ROBOCIPとしては小さい工場へもロボット導入しやすい環境を構築するところをやりたい。</t>
-    <rPh sb="41" eb="42">
-      <t>チイ</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>コウジョウ</t>
-    </rPh>
-    <rPh sb="52" eb="54">
-      <t>ドウニュウ</t>
-    </rPh>
-    <rPh sb="58" eb="60">
-      <t>カンキョウ</t>
-    </rPh>
-    <rPh sb="61" eb="63">
-      <t>コウチク</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>リスクアセスメント</t>
     <phoneticPr fontId="3"/>
   </si>
@@ -1927,6 +1910,91 @@
       <t>ショセキ</t>
     </rPh>
     <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ロングテール</t>
+  </si>
+  <si>
+    <t>販売機会の少ない商品でもアイテム数を幅広く取り揃えること。
+ロングテール市場への対応を行いたい＝小さい工場へもロボット導入しやすい環境を構築するところをやりたい</t>
+    <rPh sb="36" eb="38">
+      <t>シジョウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>チイ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>コウジョウ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>ドウニュウ</t>
+    </rPh>
+    <rPh sb="65" eb="67">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>コウチク</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>https://ja.wikipedia.org/wiki/%E3%83%AD%E3%83%B3%E3%82%B0%E3%83%86%E3%83%BC%E3%83%AB#%E9%96%A2%E9%80%A3%E9%A0%85%E7%9B%AE</t>
+  </si>
+  <si>
+    <t>リーク検査</t>
+    <rPh sb="3" eb="5">
+      <t>ケンサ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>密封性を確認し、気体や液体の漏れを検出する品質管理工程</t>
+  </si>
+  <si>
+    <t>https://www.google.com/search?q=%E3%83%AA%E3%83%BC%E3%82%AF%E6%A4%9C%E6%9F%BB&amp;oq=%E3%83%AA%E3%83%BC%E3%82%AF%E6%A4%9C%E6%9F%BB&amp;gs_lcrp=EgRlZGdlKgcIABBFGIAEMgcIABBFGIAEMgcIARAAGIAEMgcIAhAAGIAEMgcIAxAAGIAEMgcIBBAAGIAEMgcIBRAAGIAEMgcIBhAAGIAEMgcIBxAAGIAE0gEIMTA3MWowajSoAgCwAgE&amp;sourceid=chrome&amp;ie=UTF-8</t>
+  </si>
+  <si>
+    <t>ファインチューニング</t>
+  </si>
+  <si>
+    <t>機械学習の分野において、事前学習済みのモデルの一部または全部に対して再トレーニングを行い、パラメーターの微調整をすること</t>
+  </si>
+  <si>
+    <t>https://www.skygroup.jp/media/article/4090/</t>
+  </si>
+  <si>
+    <t>マテハン</t>
+  </si>
+  <si>
+    <t>マテリアル・ハンドリング</t>
+  </si>
+  <si>
+    <t>流や製造現場でモノの移動、保管、荷役、梱包を効率化する機器や作業の総称</t>
+  </si>
+  <si>
+    <t>https://www.okamura.co.jp/mhs/column/008010.html</t>
+  </si>
+  <si>
+    <t>RL</t>
+  </si>
+  <si>
+    <t>Reinforcement Learning</t>
+  </si>
+  <si>
+    <t>強化学習参照</t>
+    <rPh sb="4" eb="6">
+      <t>サンショウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
   </si>
 </sst>
 </file>
@@ -2036,7 +2104,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2078,6 +2146,36 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment vertical="top"/>
@@ -5385,7 +5483,7 @@
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
@@ -6033,43 +6131,43 @@
       </c>
     </row>
     <row r="75" spans="1:14" s="2" customFormat="1" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A75" s="3">
+      <c r="A75" s="15">
         <v>74</v>
       </c>
-      <c r="B75" s="4" t="str">
-        <f>IF(COUNTIF(用語集[キーワード],用語集[[#This Row],[キーワード]])&gt;1,"!","")</f>
-        <v/>
-      </c>
-      <c r="C75" s="4" t="str">
+      <c r="B75" s="16" t="str">
+        <f>IF(COUNTIF(用語集[キーワード],用語集[[#This Row],[キーワード]])&gt;1,"!","")</f>
+        <v/>
+      </c>
+      <c r="C75" s="16" t="str">
         <f>IF(用語集[[#This Row],[キーワード]]="","",IF(OR(用語集[[#This Row],[説明]]="",NOT(ISERROR(FIND("★",用語集[[#This Row],[説明]])))),"★","☆"))</f>
         <v>☆</v>
       </c>
-      <c r="D75" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="E75" s="3"/>
-      <c r="F75" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="G75" s="4"/>
-      <c r="H75" s="4"/>
-      <c r="I75" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="J75" s="14" t="s">
-        <v>276</v>
-      </c>
-      <c r="K75" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="L75" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="M75" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="N75" s="7" t="s">
-        <v>18</v>
+      <c r="D75" s="17" t="s">
+        <v>356</v>
+      </c>
+      <c r="E75" s="15"/>
+      <c r="F75" s="15" t="s">
+        <v>357</v>
+      </c>
+      <c r="G75" s="16"/>
+      <c r="H75" s="16"/>
+      <c r="I75" s="18" t="s">
+        <v>358</v>
+      </c>
+      <c r="J75" s="19" t="s">
+        <v>359</v>
+      </c>
+      <c r="K75" s="18" t="s">
+        <v>358</v>
+      </c>
+      <c r="L75" s="18" t="s">
+        <v>358</v>
+      </c>
+      <c r="M75" s="18" t="s">
+        <v>358</v>
+      </c>
+      <c r="N75" s="18" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="76" spans="1:14" s="2" customFormat="1" ht="22.5" x14ac:dyDescent="0.15">
@@ -6085,11 +6183,11 @@
         <v>☆</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E76" s="3"/>
       <c r="F76" s="3" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="G76" s="4"/>
       <c r="H76" s="4"/>
@@ -6097,7 +6195,7 @@
         <v>18</v>
       </c>
       <c r="J76" s="14" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="K76" s="7" t="s">
         <v>18</v>
@@ -6125,13 +6223,13 @@
         <v>☆</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="G77" s="4"/>
       <c r="H77" s="4"/>
@@ -6139,7 +6237,7 @@
         <v>18</v>
       </c>
       <c r="J77" s="14" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="K77" s="7" t="s">
         <v>18</v>
@@ -6167,11 +6265,11 @@
         <v>☆</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="G78" s="4"/>
       <c r="H78" s="4"/>
@@ -6179,7 +6277,7 @@
         <v>18</v>
       </c>
       <c r="J78" s="14" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="K78" s="7" t="s">
         <v>18</v>
@@ -6207,11 +6305,11 @@
         <v>☆</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="3" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="G79" s="4"/>
       <c r="H79" s="4"/>
@@ -6219,7 +6317,7 @@
         <v>18</v>
       </c>
       <c r="J79" s="14" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="K79" s="7" t="s">
         <v>18</v>
@@ -6247,19 +6345,19 @@
         <v>☆</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="3" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="G80" s="4"/>
       <c r="H80" s="4"/>
       <c r="I80" s="14" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="J80" s="14" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="K80" s="7" t="s">
         <v>18</v>
@@ -6287,19 +6385,19 @@
         <v>☆</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="G81" s="4"/>
       <c r="H81" s="4"/>
       <c r="I81" s="14" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J81" s="14" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="K81" s="7" t="s">
         <v>18</v>
@@ -6327,11 +6425,11 @@
         <v>☆</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="3" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G82" s="4"/>
       <c r="H82" s="4"/>
@@ -6339,7 +6437,7 @@
         <v>18</v>
       </c>
       <c r="J82" s="14" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="K82" s="7" t="s">
         <v>18</v>
@@ -6367,11 +6465,11 @@
         <v>☆</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="G83" s="4"/>
       <c r="H83" s="4"/>
@@ -6379,7 +6477,7 @@
         <v>18</v>
       </c>
       <c r="J83" s="14" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="K83" s="7" t="s">
         <v>18</v>
@@ -6407,13 +6505,13 @@
         <v>☆</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G84" s="4"/>
       <c r="H84" s="4"/>
@@ -6421,7 +6519,7 @@
         <v>18</v>
       </c>
       <c r="J84" s="14" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="K84" s="7" t="s">
         <v>18</v>
@@ -6449,21 +6547,21 @@
         <v>☆</v>
       </c>
       <c r="D85" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="F85" s="3" t="s">
         <v>305</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="F85" s="3" t="s">
-        <v>308</v>
       </c>
       <c r="G85" s="4"/>
       <c r="H85" s="4"/>
       <c r="I85" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="J85" s="14" t="s">
         <v>304</v>
-      </c>
-      <c r="J85" s="14" t="s">
-        <v>307</v>
       </c>
       <c r="K85" s="7" t="s">
         <v>18</v>
@@ -6491,19 +6589,19 @@
         <v>☆</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="E86" s="3"/>
       <c r="F86" s="3" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="G86" s="4"/>
       <c r="H86" s="4"/>
       <c r="I86" s="14" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J86" s="14" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="K86" s="7" t="s">
         <v>18</v>
@@ -6531,19 +6629,19 @@
         <v>☆</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="E87" s="3"/>
       <c r="F87" s="3" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="G87" s="4"/>
       <c r="H87" s="4"/>
       <c r="I87" s="7" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="J87" s="14" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="K87" s="7" t="s">
         <v>18</v>
@@ -6571,11 +6669,11 @@
         <v>☆</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="E88" s="3"/>
       <c r="F88" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="G88" s="4"/>
       <c r="H88" s="4"/>
@@ -6583,7 +6681,7 @@
         <v>18</v>
       </c>
       <c r="J88" s="14" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="K88" s="7" t="s">
         <v>18</v>
@@ -6611,13 +6709,13 @@
         <v>☆</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="G89" s="4"/>
       <c r="H89" s="4"/>
@@ -6625,7 +6723,7 @@
         <v>18</v>
       </c>
       <c r="J89" s="14" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="K89" s="7" t="s">
         <v>18</v>
@@ -6653,11 +6751,11 @@
         <v>☆</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E90" s="3"/>
       <c r="F90" s="3" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="G90" s="4"/>
       <c r="H90" s="4"/>
@@ -6665,7 +6763,7 @@
         <v>18</v>
       </c>
       <c r="J90" s="14" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="K90" s="7" t="s">
         <v>18</v>
@@ -6693,21 +6791,21 @@
         <v>☆</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G91" s="4"/>
       <c r="H91" s="4"/>
       <c r="I91" s="14" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="J91" s="14" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="K91" s="7" t="s">
         <v>18</v>
@@ -6735,13 +6833,13 @@
         <v>☆</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="G92" s="4"/>
       <c r="H92" s="4"/>
@@ -6749,7 +6847,7 @@
         <v>18</v>
       </c>
       <c r="J92" s="14" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="K92" s="7" t="s">
         <v>18</v>
@@ -6777,11 +6875,11 @@
         <v>☆</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="E93" s="3"/>
       <c r="F93" s="3" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="G93" s="4"/>
       <c r="H93" s="4"/>
@@ -6789,7 +6887,7 @@
         <v>18</v>
       </c>
       <c r="J93" s="14" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="K93" s="7" t="s">
         <v>18</v>
@@ -6817,19 +6915,19 @@
         <v>☆</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="E94" s="3"/>
       <c r="F94" s="3" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="G94" s="4"/>
       <c r="H94" s="4"/>
       <c r="I94" s="14" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="J94" s="14" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="K94" s="7" t="s">
         <v>18</v>
@@ -6857,21 +6955,21 @@
         <v>☆</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="G95" s="4"/>
       <c r="H95" s="4"/>
       <c r="I95" s="14" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="J95" s="14" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="K95" s="7" t="s">
         <v>18</v>
@@ -6899,19 +6997,19 @@
         <v>☆</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E96" s="3"/>
       <c r="F96" s="3" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="G96" s="4"/>
       <c r="H96" s="4"/>
       <c r="I96" s="14" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="J96" s="14" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="K96" s="7" t="s">
         <v>18</v>
@@ -6939,19 +7037,19 @@
         <v>☆</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E97" s="3"/>
       <c r="F97" s="3" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="G97" s="4"/>
       <c r="H97" s="4"/>
       <c r="I97" s="7" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="J97" s="7" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="K97" s="7" t="s">
         <v>18</v>
@@ -6979,19 +7077,19 @@
         <v>☆</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="E98" s="3"/>
       <c r="F98" s="3" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="G98" s="4"/>
       <c r="H98" s="4"/>
       <c r="I98" s="7" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="J98" s="7" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="K98" s="7" t="s">
         <v>18</v>
@@ -7016,18 +7114,22 @@
       </c>
       <c r="C99" s="4" t="str">
         <f>IF(用語集[[#This Row],[キーワード]]="","",IF(OR(用語集[[#This Row],[説明]]="",NOT(ISERROR(FIND("★",用語集[[#This Row],[説明]])))),"★","☆"))</f>
-        <v/>
-      </c>
-      <c r="D99" s="5"/>
-      <c r="E99" s="3"/>
-      <c r="F99" s="3"/>
-      <c r="G99" s="4"/>
-      <c r="H99" s="4"/>
-      <c r="I99" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="J99" s="7" t="s">
-        <v>18</v>
+        <v>☆</v>
+      </c>
+      <c r="D99" s="22" t="s">
+        <v>360</v>
+      </c>
+      <c r="E99" s="20"/>
+      <c r="F99" s="20" t="s">
+        <v>361</v>
+      </c>
+      <c r="G99" s="21"/>
+      <c r="H99" s="21"/>
+      <c r="I99" s="23" t="s">
+        <v>358</v>
+      </c>
+      <c r="J99" s="24" t="s">
+        <v>362</v>
       </c>
       <c r="K99" s="7" t="s">
         <v>18</v>
@@ -7042,7 +7144,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="100" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:14" s="2" customFormat="1" ht="22.5" x14ac:dyDescent="0.15">
       <c r="A100" s="3">
         <v>99</v>
       </c>
@@ -7052,18 +7154,22 @@
       </c>
       <c r="C100" s="4" t="str">
         <f>IF(用語集[[#This Row],[キーワード]]="","",IF(OR(用語集[[#This Row],[説明]]="",NOT(ISERROR(FIND("★",用語集[[#This Row],[説明]])))),"★","☆"))</f>
-        <v/>
-      </c>
-      <c r="D100" s="5"/>
-      <c r="E100" s="3"/>
-      <c r="F100" s="3"/>
-      <c r="G100" s="4"/>
-      <c r="H100" s="4"/>
-      <c r="I100" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="J100" s="7" t="s">
-        <v>18</v>
+        <v>☆</v>
+      </c>
+      <c r="D100" s="22" t="s">
+        <v>363</v>
+      </c>
+      <c r="E100" s="20"/>
+      <c r="F100" s="20" t="s">
+        <v>364</v>
+      </c>
+      <c r="G100" s="21"/>
+      <c r="H100" s="21"/>
+      <c r="I100" s="23" t="s">
+        <v>358</v>
+      </c>
+      <c r="J100" s="24" t="s">
+        <v>365</v>
       </c>
       <c r="K100" s="7" t="s">
         <v>18</v>
@@ -7088,18 +7194,24 @@
       </c>
       <c r="C101" s="4" t="str">
         <f>IF(用語集[[#This Row],[キーワード]]="","",IF(OR(用語集[[#This Row],[説明]]="",NOT(ISERROR(FIND("★",用語集[[#This Row],[説明]])))),"★","☆"))</f>
-        <v/>
-      </c>
-      <c r="D101" s="5"/>
-      <c r="E101" s="3"/>
-      <c r="F101" s="3"/>
-      <c r="G101" s="4"/>
-      <c r="H101" s="4"/>
-      <c r="I101" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="J101" s="7" t="s">
-        <v>18</v>
+        <v>☆</v>
+      </c>
+      <c r="D101" s="22" t="s">
+        <v>366</v>
+      </c>
+      <c r="E101" s="20" t="s">
+        <v>367</v>
+      </c>
+      <c r="F101" s="20" t="s">
+        <v>368</v>
+      </c>
+      <c r="G101" s="21"/>
+      <c r="H101" s="21"/>
+      <c r="I101" s="23" t="s">
+        <v>358</v>
+      </c>
+      <c r="J101" s="24" t="s">
+        <v>369</v>
       </c>
       <c r="K101" s="7" t="s">
         <v>18</v>
@@ -7124,18 +7236,24 @@
       </c>
       <c r="C102" s="4" t="str">
         <f>IF(用語集[[#This Row],[キーワード]]="","",IF(OR(用語集[[#This Row],[説明]]="",NOT(ISERROR(FIND("★",用語集[[#This Row],[説明]])))),"★","☆"))</f>
-        <v/>
-      </c>
-      <c r="D102" s="5"/>
-      <c r="E102" s="3"/>
-      <c r="F102" s="3"/>
-      <c r="G102" s="4"/>
-      <c r="H102" s="4"/>
-      <c r="I102" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="J102" s="7" t="s">
-        <v>18</v>
+        <v>☆</v>
+      </c>
+      <c r="D102" s="22" t="s">
+        <v>370</v>
+      </c>
+      <c r="E102" s="20" t="s">
+        <v>371</v>
+      </c>
+      <c r="F102" s="20" t="s">
+        <v>372</v>
+      </c>
+      <c r="G102" s="21"/>
+      <c r="H102" s="21"/>
+      <c r="I102" s="23" t="s">
+        <v>358</v>
+      </c>
+      <c r="J102" s="23" t="s">
+        <v>358</v>
       </c>
       <c r="K102" s="7" t="s">
         <v>18</v>
@@ -21649,41 +21767,44 @@
     <hyperlink ref="J72" r:id="rId94" xr:uid="{3AF3E0EB-466C-4652-AAF4-3659DDD11CA6}"/>
     <hyperlink ref="J73" r:id="rId95" xr:uid="{08D01DEB-F40F-4FD8-80C2-9B2679C50C5B}"/>
     <hyperlink ref="J74" r:id="rId96" xr:uid="{8CE63792-D616-4083-9D4A-055D269F8E7A}"/>
-    <hyperlink ref="J75" r:id="rId97" location="%E9%96%A2%E9%80%A3%E9%A0%85%E7%9B%AE" xr:uid="{14D572F0-62FD-4077-9807-2508EE87ECC0}"/>
-    <hyperlink ref="J76" r:id="rId98" xr:uid="{A5003D36-27B5-44B0-9231-791E46C42133}"/>
-    <hyperlink ref="J77" r:id="rId99" xr:uid="{B0080DCE-647F-4A7F-AC9D-BE4FDB04BA22}"/>
-    <hyperlink ref="J78" r:id="rId100" xr:uid="{1C8601C9-86EB-42FD-9FC9-140FABB816AC}"/>
-    <hyperlink ref="J79" r:id="rId101" xr:uid="{0DE5AE03-BE28-4DA5-866E-2BFFF20A41AC}"/>
-    <hyperlink ref="J80" r:id="rId102" xr:uid="{41F9F85E-22C0-4B5D-8BDA-701124597843}"/>
-    <hyperlink ref="I80" r:id="rId103" xr:uid="{BE0F911B-97F0-4974-88CD-2C661B5C7A8E}"/>
-    <hyperlink ref="I81" r:id="rId104" xr:uid="{6BCCBD49-AF16-45BF-8BC3-3D88C1D72DB0}"/>
-    <hyperlink ref="J81" r:id="rId105" xr:uid="{00B32316-A4BF-4D6A-A07C-6354A67939C2}"/>
-    <hyperlink ref="J82" r:id="rId106" xr:uid="{F54A4795-B5E2-490E-9721-56E958E985A8}"/>
-    <hyperlink ref="J83" r:id="rId107" xr:uid="{93FA9DC4-17C6-4E0A-8005-9F19AF79955B}"/>
-    <hyperlink ref="J84" r:id="rId108" xr:uid="{650C60BB-6D8D-4274-BD60-C7D5DA85B520}"/>
-    <hyperlink ref="J85" r:id="rId109" xr:uid="{2EB75A41-180B-41E5-9795-25809E2AA172}"/>
-    <hyperlink ref="I85" r:id="rId110" xr:uid="{183F9A5E-CE30-4993-BC22-F53FFB85D8DF}"/>
-    <hyperlink ref="J86" r:id="rId111" xr:uid="{131FC967-64BA-45F9-99D8-B9B5D38E19C8}"/>
-    <hyperlink ref="I86" r:id="rId112" xr:uid="{3A307DF4-8DD3-43C8-8F6F-E4BEF1BB30ED}"/>
-    <hyperlink ref="J87" r:id="rId113" xr:uid="{51B475F2-DFBE-4D13-AA23-561D76644DB3}"/>
-    <hyperlink ref="J88" r:id="rId114" xr:uid="{A7930026-EE68-43FE-BC46-7396B9FE3A7D}"/>
-    <hyperlink ref="J89" r:id="rId115" xr:uid="{EBCDF0E1-84A8-4464-A49E-56F30D110EC9}"/>
-    <hyperlink ref="J90" r:id="rId116" xr:uid="{D797E633-795C-4A91-9857-848CBC67B76B}"/>
-    <hyperlink ref="I91" r:id="rId117" xr:uid="{97405A7D-8C89-4FBF-ADC5-5218B78721B0}"/>
-    <hyperlink ref="J91" r:id="rId118" xr:uid="{83AED62C-3F4F-4A42-A75F-79FE7A20539B}"/>
-    <hyperlink ref="J92" r:id="rId119" xr:uid="{AF00BEB4-479E-4820-8E61-68B70E73A9D0}"/>
-    <hyperlink ref="J93" r:id="rId120" xr:uid="{70D8A915-7476-4BAB-9D5B-7D6BBA7667DA}"/>
-    <hyperlink ref="J94" r:id="rId121" xr:uid="{0C843CB9-EE25-4E25-B38C-77E44ED20985}"/>
-    <hyperlink ref="I94" r:id="rId122" xr:uid="{C5EB1502-BA39-4871-A1C5-82E76265EDBE}"/>
-    <hyperlink ref="J95" r:id="rId123" xr:uid="{CC56280C-9BA7-42B2-93E1-7363BB38CD72}"/>
-    <hyperlink ref="I95" r:id="rId124" xr:uid="{4F402C44-D1BE-4747-9847-86CC2247AAB5}"/>
-    <hyperlink ref="J96" r:id="rId125" xr:uid="{81150C89-9381-4612-8118-6ECA4EA1EF62}"/>
-    <hyperlink ref="I96" r:id="rId126" xr:uid="{AF900C4F-2035-47D1-BF8B-5F8DDE3B7095}"/>
+    <hyperlink ref="J76" r:id="rId97" xr:uid="{A5003D36-27B5-44B0-9231-791E46C42133}"/>
+    <hyperlink ref="J77" r:id="rId98" xr:uid="{B0080DCE-647F-4A7F-AC9D-BE4FDB04BA22}"/>
+    <hyperlink ref="J78" r:id="rId99" xr:uid="{1C8601C9-86EB-42FD-9FC9-140FABB816AC}"/>
+    <hyperlink ref="J79" r:id="rId100" xr:uid="{0DE5AE03-BE28-4DA5-866E-2BFFF20A41AC}"/>
+    <hyperlink ref="J80" r:id="rId101" xr:uid="{41F9F85E-22C0-4B5D-8BDA-701124597843}"/>
+    <hyperlink ref="I80" r:id="rId102" xr:uid="{BE0F911B-97F0-4974-88CD-2C661B5C7A8E}"/>
+    <hyperlink ref="I81" r:id="rId103" xr:uid="{6BCCBD49-AF16-45BF-8BC3-3D88C1D72DB0}"/>
+    <hyperlink ref="J81" r:id="rId104" xr:uid="{00B32316-A4BF-4D6A-A07C-6354A67939C2}"/>
+    <hyperlink ref="J82" r:id="rId105" xr:uid="{F54A4795-B5E2-490E-9721-56E958E985A8}"/>
+    <hyperlink ref="J83" r:id="rId106" xr:uid="{93FA9DC4-17C6-4E0A-8005-9F19AF79955B}"/>
+    <hyperlink ref="J84" r:id="rId107" xr:uid="{650C60BB-6D8D-4274-BD60-C7D5DA85B520}"/>
+    <hyperlink ref="J85" r:id="rId108" xr:uid="{2EB75A41-180B-41E5-9795-25809E2AA172}"/>
+    <hyperlink ref="I85" r:id="rId109" xr:uid="{183F9A5E-CE30-4993-BC22-F53FFB85D8DF}"/>
+    <hyperlink ref="J86" r:id="rId110" xr:uid="{131FC967-64BA-45F9-99D8-B9B5D38E19C8}"/>
+    <hyperlink ref="I86" r:id="rId111" xr:uid="{3A307DF4-8DD3-43C8-8F6F-E4BEF1BB30ED}"/>
+    <hyperlink ref="J87" r:id="rId112" xr:uid="{51B475F2-DFBE-4D13-AA23-561D76644DB3}"/>
+    <hyperlink ref="J88" r:id="rId113" xr:uid="{A7930026-EE68-43FE-BC46-7396B9FE3A7D}"/>
+    <hyperlink ref="J89" r:id="rId114" xr:uid="{EBCDF0E1-84A8-4464-A49E-56F30D110EC9}"/>
+    <hyperlink ref="J90" r:id="rId115" xr:uid="{D797E633-795C-4A91-9857-848CBC67B76B}"/>
+    <hyperlink ref="I91" r:id="rId116" xr:uid="{97405A7D-8C89-4FBF-ADC5-5218B78721B0}"/>
+    <hyperlink ref="J91" r:id="rId117" xr:uid="{83AED62C-3F4F-4A42-A75F-79FE7A20539B}"/>
+    <hyperlink ref="J92" r:id="rId118" xr:uid="{AF00BEB4-479E-4820-8E61-68B70E73A9D0}"/>
+    <hyperlink ref="J93" r:id="rId119" xr:uid="{70D8A915-7476-4BAB-9D5B-7D6BBA7667DA}"/>
+    <hyperlink ref="J94" r:id="rId120" xr:uid="{0C843CB9-EE25-4E25-B38C-77E44ED20985}"/>
+    <hyperlink ref="I94" r:id="rId121" xr:uid="{C5EB1502-BA39-4871-A1C5-82E76265EDBE}"/>
+    <hyperlink ref="J95" r:id="rId122" xr:uid="{CC56280C-9BA7-42B2-93E1-7363BB38CD72}"/>
+    <hyperlink ref="I95" r:id="rId123" xr:uid="{4F402C44-D1BE-4747-9847-86CC2247AAB5}"/>
+    <hyperlink ref="J96" r:id="rId124" xr:uid="{81150C89-9381-4612-8118-6ECA4EA1EF62}"/>
+    <hyperlink ref="I96" r:id="rId125" xr:uid="{AF900C4F-2035-47D1-BF8B-5F8DDE3B7095}"/>
+    <hyperlink ref="J75" r:id="rId126" location="%E9%96%A2%E9%80%A3%E9%A0%85%E7%9B%AE" xr:uid="{14D572F0-62FD-4077-9807-2508EE87ECC0}"/>
+    <hyperlink ref="J99" r:id="rId127" display="https://www.google.com/search?q=%E3%83%AA%E3%83%BC%E3%82%AF%E6%A4%9C%E6%9F%BB&amp;oq=%E3%83%AA%E3%83%BC%E3%82%AF%E6%A4%9C%E6%9F%BB&amp;gs_lcrp=EgRlZGdlKgcIABBFGIAEMgcIABBFGIAEMgcIARAAGIAEMgcIAhAAGIAEMgcIAxAAGIAEMgcIBBAAGIAEMgcIBRAAGIAEMgcIBhAAGIAEMgcIBxAAGIAE0gEIMTA3MWowajSoAgCwAgE&amp;sourceid=chrome&amp;ie=UTF-8" xr:uid="{A266D654-0FC1-4730-8485-336785412E67}"/>
+    <hyperlink ref="J100" r:id="rId128" xr:uid="{6CE83A74-F4AA-40A2-B4D7-1EAE616B115C}"/>
+    <hyperlink ref="J101" r:id="rId129" xr:uid="{D029580D-466B-4425-AC22-5326D642FD9F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId127"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId130"/>
   <tableParts count="1">
-    <tablePart r:id="rId128"/>
+    <tablePart r:id="rId131"/>
   </tableParts>
 </worksheet>
 </file>